--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\DEV\Rapport-Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2609B1F9-4B5A-42FC-AFF0-5849027F67C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DF9BA4-EE1C-4166-BC41-6F48CB40AAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>date</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Requires follow-up visit</t>
+  </si>
+  <si>
+    <t>Spiceis</t>
   </si>
 </sst>
 </file>
@@ -148,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -161,6 +164,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="1" customWidth="1"/>
@@ -450,9 +456,10 @@
     <col min="3" max="3" width="34.85546875" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="34" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -468,8 +475,11 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="5" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>45455</v>
       </c>
@@ -486,7 +496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>45456</v>
       </c>
@@ -503,7 +513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>45457</v>
       </c>
@@ -520,7 +530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>45458</v>
       </c>
@@ -537,7 +547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>45459</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\DEV\Rapport-Generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4DF9BA4-EE1C-4166-BC41-6F48CB40AAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08478C2-9F00-4CAB-9990-8C03D690F9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>date</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Requires follow-up visit</t>
-  </si>
-  <si>
-    <t>Spiceis</t>
   </si>
 </sst>
 </file>
@@ -475,9 +472,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
